--- a/data/dividends_info_20260505.xlsx
+++ b/data/dividends_info_20260505.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.51499938964844</v>
+        <v>48.79999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1894138717375366</v>
+        <v>0.1844262323915174</v>
       </c>
       <c r="J2" t="n">
         <v>314</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.95000076293945</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.273885332631531</v>
+        <v>1.275045501902276</v>
       </c>
       <c r="J3" t="n">
         <v>293</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.640000343322754</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6224066168375152</v>
+        <v>0.6185567131938485</v>
       </c>
       <c r="J4" t="n">
         <v>223</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.51499938964844</v>
+        <v>48.79999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1894138717375366</v>
+        <v>0.1844262323915174</v>
       </c>
       <c r="J6" t="n">
         <v>223</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.069999933242798</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.719806883248261</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>202</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.78000020980835</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>3.460207486854598</v>
+        <v>3.424657444766908</v>
       </c>
       <c r="J8" t="n">
         <v>195</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.199999809265137</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9615384968074835</v>
+        <v>0.9541985149615856</v>
       </c>
       <c r="J11" t="n">
         <v>153</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.980000019073486</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J12" t="n">
         <v>146</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>47.51499938964844</v>
+        <v>48.79999923706055</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1894138717375366</v>
+        <v>0.1844262323915174</v>
       </c>
       <c r="J13" t="n">
         <v>139</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.980000019073486</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J15" t="n">
         <v>90</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.039999961853027</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="I16" t="n">
-        <v>4.139072873823361</v>
+        <v>4.111842156859978</v>
       </c>
       <c r="J16" t="n">
         <v>83</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9.729999542236328</v>
+        <v>9.710000038146973</v>
       </c>
       <c r="I17" t="n">
-        <v>2.672148121604557</v>
+        <v>2.67765189473282</v>
       </c>
       <c r="J17" t="n">
         <v>76</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>16.04000091552734</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="I18" t="n">
-        <v>3.740648165544533</v>
+        <v>3.821656097383634</v>
       </c>
       <c r="J18" t="n">
         <v>76</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.710000038146973</v>
+        <v>3.697999954223633</v>
       </c>
       <c r="I19" t="n">
-        <v>5.929919076493676</v>
+        <v>5.949161782674693</v>
       </c>
       <c r="J19" t="n">
         <v>76</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.864999771118164</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="I21" t="n">
-        <v>4.092071770946445</v>
+        <v>4.081632573621466</v>
       </c>
       <c r="J21" t="n">
         <v>76</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>18.25</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="I22" t="n">
-        <v>2.06027397260274</v>
+        <v>2.04347830323506</v>
       </c>
       <c r="J22" t="n">
         <v>76</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.570000171661377</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="I23" t="n">
-        <v>2.154398497338059</v>
+        <v>2.16998183448819</v>
       </c>
       <c r="J23" t="n">
         <v>69</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.050000190734863</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="I26" t="n">
-        <v>1.728394980329585</v>
+        <v>1.694915207271755</v>
       </c>
       <c r="J26" t="n">
         <v>62</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36.65000152587891</v>
+        <v>35.59999847412109</v>
       </c>
       <c r="I27" t="n">
-        <v>0.409276927025729</v>
+        <v>0.4213483326664756</v>
       </c>
       <c r="J27" t="n">
         <v>62</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>22.94000053405762</v>
+        <v>23.10000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>4.141237915795132</v>
+        <v>4.112554044640049</v>
       </c>
       <c r="J29" t="n">
         <v>48</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>27.20000076293945</v>
+        <v>27.25</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7169117445970495</v>
+        <v>0.7155963302752294</v>
       </c>
       <c r="J30" t="n">
         <v>48</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.949999809265137</v>
+        <v>4.938000202178955</v>
       </c>
       <c r="I32" t="n">
-        <v>5.858586084330629</v>
+        <v>5.872822764811427</v>
       </c>
       <c r="J32" t="n">
         <v>48</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3.967999935150146</v>
+        <v>3.946000099182129</v>
       </c>
       <c r="I33" t="n">
-        <v>4.032258130416166</v>
+        <v>4.054738874263144</v>
       </c>
       <c r="J33" t="n">
         <v>48</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.594000101089478</v>
+        <v>2.585999965667725</v>
       </c>
       <c r="I34" t="n">
-        <v>5.343099252069734</v>
+        <v>5.359628841457174</v>
       </c>
       <c r="J34" t="n">
         <v>48</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>53.13000106811523</v>
+        <v>53.27999877929688</v>
       </c>
       <c r="I35" t="n">
-        <v>1.185770727149637</v>
+        <v>1.182432459523254</v>
       </c>
       <c r="J35" t="n">
         <v>48</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.054999828338623</v>
+        <v>5.005000114440918</v>
       </c>
       <c r="I36" t="n">
-        <v>2.769535207798661</v>
+        <v>2.797202733243866</v>
       </c>
       <c r="J36" t="n">
         <v>48</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>22.30999946594238</v>
+        <v>22.21999931335449</v>
       </c>
       <c r="I38" t="n">
-        <v>3.809950785958459</v>
+        <v>3.825382656466329</v>
       </c>
       <c r="J38" t="n">
         <v>48</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>47.5099983215332</v>
+        <v>48.79999923706055</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1894338101022597</v>
+        <v>0.1844262323915174</v>
       </c>
       <c r="J39" t="n">
         <v>48</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6.622000217437744</v>
+        <v>6.607999801635742</v>
       </c>
       <c r="I40" t="n">
-        <v>2.737843461898141</v>
+        <v>2.743644150157526</v>
       </c>
       <c r="J40" t="n">
         <v>48</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8.619999885559082</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I41" t="n">
-        <v>3.016241339348193</v>
+        <v>3.040935604676908</v>
       </c>
       <c r="J41" t="n">
         <v>48</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10.21000003814697</v>
+        <v>10.13500022888184</v>
       </c>
       <c r="I42" t="n">
-        <v>2.713026434525589</v>
+        <v>2.73310304631893</v>
       </c>
       <c r="J42" t="n">
         <v>48</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.174999952316284</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="I43" t="n">
-        <v>1.148936216838764</v>
+        <v>1.15384619616898</v>
       </c>
       <c r="J43" t="n">
         <v>41</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.940000057220459</v>
+        <v>3.75600004196167</v>
       </c>
       <c r="I44" t="n">
-        <v>2.791878132042501</v>
+        <v>2.928647464619026</v>
       </c>
       <c r="J44" t="n">
         <v>41</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.345000028610229</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="I46" t="n">
-        <v>4.783258554005942</v>
+        <v>4.804804914888146</v>
       </c>
       <c r="J46" t="n">
         <v>34</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27.70000076293945</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="I48" t="n">
-        <v>4.007220106235873</v>
+        <v>4.043715734604362</v>
       </c>
       <c r="J48" t="n">
         <v>30</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9089999794960022</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I49" t="n">
-        <v>3.300330107447702</v>
+        <v>3.333333421636513</v>
       </c>
       <c r="J49" t="n">
         <v>27</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5059999823570251</v>
       </c>
       <c r="I50" t="n">
-        <v>4.509804005899691</v>
+        <v>4.545454703943365</v>
       </c>
       <c r="J50" t="n">
         <v>27</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>19.14999961853027</v>
+        <v>19.25</v>
       </c>
       <c r="I51" t="n">
-        <v>3.13315933134232</v>
+        <v>3.116883116883117</v>
       </c>
       <c r="J51" t="n">
         <v>27</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.559999942779541</v>
+        <v>2.525000095367432</v>
       </c>
       <c r="I53" t="n">
-        <v>7.031250157160687</v>
+        <v>7.128712602040787</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13.35000038146973</v>
+        <v>13.22000026702881</v>
       </c>
       <c r="I55" t="n">
-        <v>1.872659122519643</v>
+        <v>1.891074091908377</v>
       </c>
       <c r="J55" t="n">
         <v>20</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.390000104904175</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8849557248272714</v>
+        <v>0.8797653737504787</v>
       </c>
       <c r="J56" t="n">
         <v>20</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3.740000009536743</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="I57" t="n">
-        <v>4.010695176938778</v>
+        <v>4.04312664306387</v>
       </c>
       <c r="J57" t="n">
         <v>20</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13.5</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="I58" t="n">
-        <v>4.296296296296296</v>
+        <v>4.249084367831286</v>
       </c>
       <c r="J58" t="n">
         <v>20</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.384000062942505</v>
+        <v>2.375999927520752</v>
       </c>
       <c r="I59" t="n">
-        <v>4.362415992205793</v>
+        <v>4.377104510626785</v>
       </c>
       <c r="J59" t="n">
         <v>13</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.522000312805176</v>
+        <v>9.977999687194824</v>
       </c>
       <c r="I60" t="n">
-        <v>3.045578559895743</v>
+        <v>2.906394158061248</v>
       </c>
       <c r="J60" t="n">
         <v>13</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.069999933242798</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I61" t="n">
-        <v>3.719806883248261</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J61" t="n">
         <v>13</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>37.90000152587891</v>
+        <v>38.25</v>
       </c>
       <c r="I62" t="n">
-        <v>4.327176606787664</v>
+        <v>4.287581699346405</v>
       </c>
       <c r="J62" t="n">
         <v>13</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>35.91999816894531</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="I63" t="n">
-        <v>5.567929014342498</v>
+        <v>5.491488469390876</v>
       </c>
       <c r="J63" t="n">
         <v>13</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.924000024795532</v>
+        <v>3.914000034332275</v>
       </c>
       <c r="I64" t="n">
-        <v>2.54841996350932</v>
+        <v>2.55493099445156</v>
       </c>
       <c r="J64" t="n">
         <v>13</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>31.51000022888184</v>
+        <v>30.93000030517578</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4711520118109129</v>
+        <v>0.4799870628360677</v>
       </c>
       <c r="J65" t="n">
         <v>13</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>23.31999969482422</v>
+        <v>22.92000007629395</v>
       </c>
       <c r="I66" t="n">
-        <v>3.945111543908769</v>
+        <v>4.013961592223344</v>
       </c>
       <c r="J66" t="n">
         <v>13</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>8.5</v>
+        <v>8.444999694824219</v>
       </c>
       <c r="I67" t="n">
-        <v>3.529411764705882</v>
+        <v>3.552397996933787</v>
       </c>
       <c r="J67" t="n">
         <v>13</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>82.91999816894531</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="I68" t="n">
-        <v>1.254220963537713</v>
+        <v>1.263669454964603</v>
       </c>
       <c r="J68" t="n">
         <v>13</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>45.79000091552734</v>
+        <v>45.88999938964844</v>
       </c>
       <c r="I69" t="n">
-        <v>1.528718030146688</v>
+        <v>1.525386814796736</v>
       </c>
       <c r="J69" t="n">
         <v>13</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>54.95000076293945</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I70" t="n">
-        <v>4.003639616841954</v>
+        <v>4.00728586312144</v>
       </c>
       <c r="J70" t="n">
         <v>13</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9.057000160217285</v>
+        <v>9.218999862670898</v>
       </c>
       <c r="I71" t="n">
-        <v>9.49541774082698</v>
+        <v>9.328560720369113</v>
       </c>
       <c r="J71" t="n">
         <v>13</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>12.60999965667725</v>
+        <v>12.67399978637695</v>
       </c>
       <c r="I72" t="n">
-        <v>4.440920025746939</v>
+        <v>4.41849463025819</v>
       </c>
       <c r="J72" t="n">
         <v>13</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2.180000066757202</v>
+        <v>2.25</v>
       </c>
       <c r="I73" t="n">
-        <v>1.834862329132901</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="J73" t="n">
         <v>13</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>10</v>
+        <v>9.789999961853027</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>3.06435139089844</v>
       </c>
       <c r="J74" t="n">
         <v>13</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>82.30000305175781</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="I76" t="n">
-        <v>2.503037574256811</v>
+        <v>2.461170938003556</v>
       </c>
       <c r="J76" t="n">
         <v>13</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.09000015258789</v>
+        <v>15.0600004196167</v>
       </c>
       <c r="I77" t="n">
-        <v>4.970178876183624</v>
+        <v>4.980079542514971</v>
       </c>
       <c r="J77" t="n">
         <v>13</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>15.10999965667725</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I78" t="n">
-        <v>1.985440151002434</v>
+        <v>1.981505899584144</v>
       </c>
       <c r="J78" t="n">
         <v>13</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>46.09999847412109</v>
+        <v>46</v>
       </c>
       <c r="I79" t="n">
-        <v>1.843817848447782</v>
+        <v>1.847826086956522</v>
       </c>
       <c r="J79" t="n">
         <v>13</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>33.29999923706055</v>
+        <v>33.41999816894531</v>
       </c>
       <c r="I80" t="n">
-        <v>2.552552611034327</v>
+        <v>2.543387332647555</v>
       </c>
       <c r="J80" t="n">
         <v>13</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>61.70000076293945</v>
+        <v>61.90000152587891</v>
       </c>
       <c r="I81" t="n">
-        <v>2.106969179781363</v>
+        <v>2.100161499118059</v>
       </c>
       <c r="J81" t="n">
         <v>13</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>8.119999885559082</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I82" t="n">
-        <v>7.389162665717064</v>
+        <v>7.407407058555364</v>
       </c>
       <c r="J82" t="n">
         <v>13</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.949999809265137</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
-        <v>7.899159917083225</v>
+        <v>7.833333333333332</v>
       </c>
       <c r="J83" t="n">
         <v>13</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5.78000020980835</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I84" t="n">
-        <v>3.460207486854598</v>
+        <v>3.424657444766908</v>
       </c>
       <c r="J84" t="n">
         <v>13</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22.94000053405762</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="I85" t="n">
-        <v>4.35919780610014</v>
+        <v>4.397537423329659</v>
       </c>
       <c r="J85" t="n">
         <v>13</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.760000228881836</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="I86" t="n">
-        <v>4.516806505501057</v>
+        <v>4.574468270746932</v>
       </c>
       <c r="J86" t="n">
         <v>13</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>24.04000091552734</v>
+        <v>23.96500015258789</v>
       </c>
       <c r="I87" t="n">
-        <v>1.123128077027685</v>
+        <v>1.126643013898933</v>
       </c>
       <c r="J87" t="n">
         <v>13</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8.159999847412109</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="I88" t="n">
-        <v>2.450980437988963</v>
+        <v>2.457002353372873</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>9.274999618530273</v>
+        <v>9.194999694824219</v>
       </c>
       <c r="I89" t="n">
-        <v>2.587601184592077</v>
+        <v>2.610114279123835</v>
       </c>
       <c r="J89" t="n">
         <v>13</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>21.05999946594238</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="I90" t="n">
-        <v>3.751187179646253</v>
+        <v>3.75296925716334</v>
       </c>
       <c r="J90" t="n">
         <v>13</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5.159999847412109</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I91" t="n">
-        <v>1.802325634692455</v>
+        <v>1.788461604061919</v>
       </c>
       <c r="J91" t="n">
         <v>13</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>35.68000030517578</v>
+        <v>35.38000106811523</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9809416956457497</v>
+        <v>0.9892594387607948</v>
       </c>
       <c r="J93" t="n">
         <v>13</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>7.329999923706055</v>
+        <v>7.170000076293945</v>
       </c>
       <c r="I94" t="n">
-        <v>7.562073748559406</v>
+        <v>7.730822790820785</v>
       </c>
       <c r="J94" t="n">
         <v>13</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>12.80000019073486</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I96" t="n">
-        <v>1.562499976716936</v>
+        <v>1.556420187258585</v>
       </c>
       <c r="J96" t="n">
         <v>13</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.114999771118164</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="I97" t="n">
-        <v>1.684382728622177</v>
+        <v>1.632329650301529</v>
       </c>
       <c r="J97" t="n">
         <v>13</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5.749000072479248</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="I98" t="n">
-        <v>3.304922553567872</v>
+        <v>3.298610980036087</v>
       </c>
       <c r="J98" t="n">
         <v>13</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>10.25</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="I99" t="n">
-        <v>4.214634146341464</v>
+        <v>4.210526221860334</v>
       </c>
       <c r="J99" t="n">
         <v>13</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>24.80999946594238</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="I100" t="n">
-        <v>1.773478474290193</v>
+        <v>1.79226074816238</v>
       </c>
       <c r="J100" t="n">
         <v>13</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1.059999942779541</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="I101" t="n">
-        <v>2.830188832023306</v>
+        <v>2.857142986894471</v>
       </c>
       <c r="J101" t="n">
         <v>13</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8.449999809265137</v>
+        <v>8.460000038146973</v>
       </c>
       <c r="I102" t="n">
-        <v>5.562130303064161</v>
+        <v>5.555555530505009</v>
       </c>
       <c r="J102" t="n">
         <v>13</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>51.34000015258789</v>
+        <v>51.7599983215332</v>
       </c>
       <c r="I103" t="n">
-        <v>2.726918573897648</v>
+        <v>2.704791432378335</v>
       </c>
       <c r="J103" t="n">
         <v>13</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>4.168000221252441</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="I104" t="n">
-        <v>7.197696354964517</v>
+        <v>7.334963051533854</v>
       </c>
       <c r="J104" t="n">
         <v>13</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>12.69999980926514</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9448819039544819</v>
+        <v>0.9523809235472627</v>
       </c>
       <c r="J105" t="n">
         <v>13</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3.400000095367432</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="I106" t="n">
-        <v>4.999999859753782</v>
+        <v>4.927536163778773</v>
       </c>
       <c r="J106" t="n">
         <v>13</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.95000076293945</v>
+        <v>21.85000038146973</v>
       </c>
       <c r="I107" t="n">
-        <v>3.189065948379762</v>
+        <v>3.203661271299781</v>
       </c>
       <c r="J107" t="n">
         <v>13</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2.5</v>
+        <v>2.460000038146973</v>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>1.422764205579615</v>
       </c>
       <c r="J108" t="n">
         <v>13</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>6.179999828338623</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I109" t="n">
-        <v>5.339805973566092</v>
+        <v>5.44554460587402</v>
       </c>
       <c r="J109" t="n">
         <v>13</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9670000076293945</v>
+        <v>0.968999981880188</v>
       </c>
       <c r="I110" t="n">
-        <v>7.238883086630513</v>
+        <v>7.223942343546416</v>
       </c>
       <c r="J110" t="n">
         <v>13</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>49.91999816894531</v>
+        <v>49.29999923706055</v>
       </c>
       <c r="I111" t="n">
-        <v>1.422275693194403</v>
+        <v>1.440162294092427</v>
       </c>
       <c r="J111" t="n">
         <v>13</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>97.19999694824219</v>
+        <v>96.90000152587891</v>
       </c>
       <c r="I112" t="n">
-        <v>1.388888932495398</v>
+        <v>1.393188832550697</v>
       </c>
       <c r="J112" t="n">
         <v>13</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>4.64300012588501</v>
+        <v>4.651999950408936</v>
       </c>
       <c r="I115" t="n">
-        <v>3.661425703011284</v>
+        <v>3.654342257356561</v>
       </c>
       <c r="J115" t="n">
         <v>13</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>56.40000152587891</v>
+        <v>56.5</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7978723188394231</v>
+        <v>0.7964601769911505</v>
       </c>
       <c r="J117" t="n">
         <v>13</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5.119999885559082</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7812500174622986</v>
+        <v>0.8032128483293034</v>
       </c>
       <c r="J118" t="n">
         <v>13</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>33.04000091552734</v>
+        <v>32.84000015258789</v>
       </c>
       <c r="I119" t="n">
-        <v>3.177966013634541</v>
+        <v>3.197320326191463</v>
       </c>
       <c r="J119" t="n">
         <v>13</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>19.79000091552734</v>
+        <v>19.38999938964844</v>
       </c>
       <c r="I121" t="n">
-        <v>1.92016160899644</v>
+        <v>1.959773140595699</v>
       </c>
       <c r="J121" t="n">
         <v>13</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>26.68000030517578</v>
+        <v>27.07999992370605</v>
       </c>
       <c r="I122" t="n">
-        <v>2.248875536495414</v>
+        <v>2.21565731791142</v>
       </c>
       <c r="J122" t="n">
         <v>13</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>34.84999847412109</v>
+        <v>33.90000152587891</v>
       </c>
       <c r="I123" t="n">
-        <v>1.004304204661308</v>
+        <v>1.032448331109406</v>
       </c>
       <c r="J123" t="n">
         <v>13</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>3.440000057220459</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4941860382914094</v>
+        <v>0.4775280975630273</v>
       </c>
       <c r="J124" t="n">
         <v>13</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.930000066757202</v>
+        <v>2.875</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3412969205515264</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="J125" t="n">
         <v>13</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>21.84000015258789</v>
+        <v>21.85000038146973</v>
       </c>
       <c r="I126" t="n">
-        <v>5.128205092376283</v>
+        <v>5.12585803407965</v>
       </c>
       <c r="J126" t="n">
         <v>13</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1.590000033378601</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I127" t="n">
-        <v>6.289308044070249</v>
+        <v>6.369426538796359</v>
       </c>
       <c r="J127" t="n">
         <v>13</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>8.600000381469727</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9418604233382281</v>
+        <v>0.9101123985595875</v>
       </c>
       <c r="J128" t="n">
         <v>13</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.20799994468689</v>
+        <v>2.130000114440918</v>
       </c>
       <c r="I129" t="n">
-        <v>4.180253727908893</v>
+        <v>4.333333100511447</v>
       </c>
       <c r="J129" t="n">
         <v>13</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9.260000228881836</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="I130" t="n">
-        <v>3.779697530766295</v>
+        <v>3.871681432266917</v>
       </c>
       <c r="J130" t="n">
         <v>6</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>5.25</v>
+        <v>5.050000190734863</v>
       </c>
       <c r="I131" t="n">
-        <v>1.828571428571429</v>
+        <v>1.900990027210877</v>
       </c>
       <c r="J131" t="n">
         <v>6</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.640000343322754</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6224066168375152</v>
+        <v>0.6185567131938485</v>
       </c>
       <c r="J134" t="n">
         <v>6</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>19.89999961853027</v>
+        <v>19.76000022888184</v>
       </c>
       <c r="I135" t="n">
-        <v>2.512562862234506</v>
+        <v>2.5303643431602</v>
       </c>
       <c r="J135" t="n">
         <v>6</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>3.680000066757202</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I139" t="n">
-        <v>2.989130380558157</v>
+        <v>3.072625763805235</v>
       </c>
       <c r="J139" t="n">
         <v>6</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>4.880000114440918</v>
+        <v>4.829999923706055</v>
       </c>
       <c r="I141" t="n">
-        <v>1.946721265822835</v>
+        <v>1.966873737072579</v>
       </c>
       <c r="J141" t="n">
         <v>6</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1.259999990463257</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="I142" t="n">
-        <v>2.380952398973438</v>
+        <v>2.362204759886205</v>
       </c>
       <c r="J142" t="n">
         <v>6</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>7.349999904632568</v>
+        <v>7.5</v>
       </c>
       <c r="I143" t="n">
-        <v>1.224489811806319</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>6</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>6.989999771118164</v>
+        <v>6.929999828338623</v>
       </c>
       <c r="I145" t="n">
-        <v>3.147353465003153</v>
+        <v>3.174603253240515</v>
       </c>
       <c r="J145" t="n">
         <v>6</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>27.45000076293945</v>
+        <v>26.54999923706055</v>
       </c>
       <c r="I146" t="n">
-        <v>2.222222160458253</v>
+        <v>2.297551855099546</v>
       </c>
       <c r="J146" t="n">
         <v>-1</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>2.930000066757202</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="I147" t="n">
-        <v>5.119453808272897</v>
+        <v>4.918032863773797</v>
       </c>
       <c r="J147" t="n">
         <v>-1</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>11.64999961853027</v>
+        <v>11.5</v>
       </c>
       <c r="I148" t="n">
-        <v>6.008583887733292</v>
+        <v>6.08695652173913</v>
       </c>
       <c r="J148" t="n">
         <v>-1</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>8.074999809265137</v>
+        <v>8.225000381469727</v>
       </c>
       <c r="I150" t="n">
-        <v>3.343653329752478</v>
+        <v>3.28267461978833</v>
       </c>
       <c r="J150" t="n">
         <v>-1</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>5.579999923706055</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I151" t="n">
-        <v>6.272401519452734</v>
+        <v>6.151142293150934</v>
       </c>
       <c r="J151" t="n">
         <v>-1</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>40</v>
+        <v>39.40000152587891</v>
       </c>
       <c r="I152" t="n">
-        <v>2.75</v>
+        <v>2.791878064465283</v>
       </c>
       <c r="J152" t="n">
         <v>-1</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>17.85000038146973</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="I153" t="n">
-        <v>4.20168058247541</v>
+        <v>4.213483326664756</v>
       </c>
       <c r="J153" t="n">
         <v>-1</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11.75</v>
+        <v>11.64999961853027</v>
       </c>
       <c r="I154" t="n">
-        <v>3.659574468085106</v>
+        <v>3.690987245321879</v>
       </c>
       <c r="J154" t="n">
         <v>-1</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.26000022888184</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="I156" t="n">
-        <v>1.608229986289182</v>
+        <v>1.648570228855522</v>
       </c>
       <c r="J156" t="n">
         <v>-1</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>28.10000038146973</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="I157" t="n">
-        <v>3.914590694188689</v>
+        <v>3.907637708371066</v>
       </c>
       <c r="J157" t="n">
         <v>-1</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>54.20000076293945</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8671586593802665</v>
+        <v>0.8131487996606106</v>
       </c>
       <c r="J158" t="n">
         <v>-1</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>79.5</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="I159" t="n">
-        <v>1.509433962264151</v>
+        <v>1.536491707355958</v>
       </c>
       <c r="J159" t="n">
         <v>-1</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>26</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="I160" t="n">
-        <v>1.038461538461539</v>
+        <v>1.060903701005686</v>
       </c>
       <c r="J160" t="n">
         <v>-1</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>10.5</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I161" t="n">
-        <v>3.619047619047619</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J161" t="n">
         <v>-1</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>30.39999961853027</v>
+        <v>29.95000076293945</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9868421176463945</v>
+        <v>1.001669423565505</v>
       </c>
       <c r="J162" t="n">
         <v>-1</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>0.1850000023841858</v>
+        <v>0.1835999935865402</v>
       </c>
       <c r="I163" t="n">
-        <v>3.783783735020306</v>
+        <v>3.812636298759203</v>
       </c>
       <c r="J163" t="n">
         <v>-8</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>7.420000076293945</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I164" t="n">
-        <v>2.156334209634064</v>
+        <v>2.247191047355422</v>
       </c>
       <c r="J164" t="n">
         <v>-8</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>2.174999952316284</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I165" t="n">
-        <v>2.988505812645086</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J165" t="n">
         <v>-8</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>7.550000190734863</v>
+        <v>7.409999847412109</v>
       </c>
       <c r="I166" t="n">
-        <v>3.311258194493725</v>
+        <v>3.373819232767066</v>
       </c>
       <c r="J166" t="n">
         <v>-8</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1.389999985694885</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I167" t="n">
-        <v>5.035971274849027</v>
+        <v>5.109489033310991</v>
       </c>
       <c r="J167" t="n">
         <v>-8</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>6.920000076293945</v>
+        <v>6.889999866485596</v>
       </c>
       <c r="I168" t="n">
-        <v>7.22543344635017</v>
+        <v>7.256894189970958</v>
       </c>
       <c r="J168" t="n">
         <v>-15</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>18.58499908447266</v>
+        <v>18.51499938964844</v>
       </c>
       <c r="I169" t="n">
-        <v>3.497444347700077</v>
+        <v>3.510667142465092</v>
       </c>
       <c r="J169" t="n">
         <v>-15</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>12.41499996185303</v>
+        <v>12.30500030517578</v>
       </c>
       <c r="I170" t="n">
-        <v>4.349577137810971</v>
+        <v>4.388459866781661</v>
       </c>
       <c r="J170" t="n">
         <v>-15</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>6.354000091552734</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="I171" t="n">
-        <v>1.57381174943551</v>
+        <v>1.57480317325747</v>
       </c>
       <c r="J171" t="n">
         <v>-15</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>9.319999694824219</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I172" t="n">
-        <v>1.716738253638083</v>
+        <v>1.739130470838349</v>
       </c>
       <c r="J172" t="n">
         <v>-15</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>293.9500122070312</v>
+        <v>279.5499877929688</v>
       </c>
       <c r="I173" t="n">
-        <v>1.229800935491688</v>
+        <v>1.293149761350455</v>
       </c>
       <c r="J173" t="n">
         <v>-15</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>30.79999923706055</v>
+        <v>30.5</v>
       </c>
       <c r="I174" t="n">
-        <v>4.415584524961806</v>
+        <v>4.459016393442623</v>
       </c>
       <c r="J174" t="n">
         <v>-15</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>15.81999969482422</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="I176" t="n">
-        <v>3.697850893078036</v>
+        <v>3.667711642605673</v>
       </c>
       <c r="J176" t="n">
         <v>-15</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>19.94000053405762</v>
+        <v>20.09000015258789</v>
       </c>
       <c r="I177" t="n">
-        <v>3.159478350684881</v>
+        <v>3.13588847792441</v>
       </c>
       <c r="J177" t="n">
         <v>-15</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>129.9499969482422</v>
+        <v>139.6000061035156</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6925740832133003</v>
+        <v>0.6446991122139606</v>
       </c>
       <c r="J178" t="n">
         <v>-15</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>66.51000213623047</v>
+        <v>67.81999969482422</v>
       </c>
       <c r="I179" t="n">
-        <v>2.587280025153715</v>
+        <v>2.537304641320023</v>
       </c>
       <c r="J179" t="n">
         <v>-15</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>26.79999923706055</v>
+        <v>26.5</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5223880745727789</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="J180" t="n">
         <v>-22</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1.519999980926514</v>
+        <v>1.5</v>
       </c>
       <c r="I181" t="n">
-        <v>3.947368470585578</v>
+        <v>4</v>
       </c>
       <c r="J181" t="n">
         <v>-22</v>
@@ -9713,7 +9713,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9774,14 +9774,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9798,7 +9798,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9808,14 +9808,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9825,14 +9825,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9849,7 +9849,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9893,14 +9893,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9910,14 +9910,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9927,14 +9927,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10029,14 +10029,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10053,7 +10053,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10097,14 +10097,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10155,7 +10155,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10165,14 +10165,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10189,7 +10189,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10206,7 +10206,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10216,14 +10216,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10240,7 +10240,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10250,14 +10250,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10284,14 +10284,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10325,7 +10325,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10335,14 +10335,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10359,7 +10359,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10369,14 +10369,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10386,14 +10386,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10410,7 +10410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10437,14 +10437,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10454,14 +10454,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10505,14 +10505,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10648,7 +10648,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10811,14 +10811,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10835,7 +10835,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10852,7 +10852,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10869,7 +10869,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10879,14 +10879,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10896,14 +10896,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10913,14 +10913,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10930,14 +10930,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10971,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10981,14 +10981,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11015,14 +11015,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11032,14 +11032,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11049,14 +11049,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11066,14 +11066,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11090,7 +11090,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11107,7 +11107,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11168,14 +11168,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11185,14 +11185,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11202,14 +11202,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11226,7 +11226,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11236,14 +11236,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11253,14 +11253,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11277,7 +11277,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11311,7 +11311,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11321,14 +11321,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11338,14 +11338,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11355,14 +11355,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11379,7 +11379,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11396,7 +11396,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11406,14 +11406,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11430,7 +11430,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11447,7 +11447,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11457,14 +11457,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11481,7 +11481,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,14 +11491,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11515,7 +11515,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11525,14 +11525,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11549,7 +11549,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11559,14 +11559,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11576,14 +11576,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11600,7 +11600,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11617,7 +11617,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11661,14 +11661,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11685,7 +11685,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11712,14 +11712,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11729,14 +11729,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11763,14 +11763,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11787,7 +11787,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11804,7 +11804,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11821,7 +11821,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11831,14 +11831,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11872,7 +11872,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11882,14 +11882,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11906,7 +11906,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11916,14 +11916,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11940,7 +11940,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11957,7 +11957,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11974,7 +11974,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12001,14 +12001,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12025,7 +12025,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12042,7 +12042,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12059,7 +12059,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12093,7 +12093,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12110,7 +12110,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12127,7 +12127,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12144,7 +12144,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12154,14 +12154,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12178,7 +12178,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12195,7 +12195,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12222,14 +12222,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12239,14 +12239,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12256,14 +12256,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12280,7 +12280,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12307,14 +12307,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12331,7 +12331,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12375,14 +12375,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12392,14 +12392,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12416,7 +12416,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12426,14 +12426,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12443,14 +12443,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12467,7 +12467,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12484,7 +12484,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12494,14 +12494,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12511,14 +12511,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12528,14 +12528,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12545,14 +12545,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12569,7 +12569,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12586,7 +12586,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12603,7 +12603,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12620,7 +12620,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12637,7 +12637,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12671,7 +12671,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12688,7 +12688,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12698,14 +12698,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12715,14 +12715,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12739,7 +12739,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12756,7 +12756,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12766,14 +12766,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12783,14 +12783,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12800,14 +12800,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12824,7 +12824,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12834,14 +12834,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12858,7 +12858,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12885,14 +12885,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12902,14 +12902,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12919,14 +12919,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12943,7 +12943,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12977,7 +12977,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12994,7 +12994,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13011,7 +13011,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13028,7 +13028,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13079,7 +13079,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13089,14 +13089,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13106,14 +13106,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13164,7 +13164,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13198,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13215,7 +13215,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13232,7 +13232,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13249,7 +13249,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13259,14 +13259,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13276,14 +13276,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13293,14 +13293,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13310,14 +13310,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13327,14 +13327,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13351,7 +13351,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13361,14 +13361,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13378,14 +13378,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13395,14 +13395,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13412,14 +13412,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13429,14 +13429,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13446,14 +13446,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13463,14 +13463,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13480,14 +13480,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13497,14 +13497,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13555,7 +13555,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13565,14 +13565,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13582,14 +13582,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13599,14 +13599,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13616,14 +13616,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13674,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13691,7 +13691,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13701,14 +13701,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13752,14 +13752,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13776,7 +13776,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13793,7 +13793,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13803,14 +13803,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13827,7 +13827,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13844,7 +13844,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13861,7 +13861,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13888,14 +13888,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13912,7 +13912,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13922,14 +13922,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13956,14 +13956,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13973,14 +13973,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13990,14 +13990,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -14024,14 +14024,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -14048,7 +14048,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14058,14 +14058,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14099,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14109,14 +14109,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14126,14 +14126,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14143,14 +14143,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14160,14 +14160,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14177,14 +14177,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14201,7 +14201,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14211,14 +14211,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14252,7 +14252,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14262,14 +14262,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14286,7 +14286,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14303,7 +14303,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14313,14 +14313,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14337,7 +14337,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14347,14 +14347,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14364,14 +14364,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14381,14 +14381,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14398,14 +14398,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14415,14 +14415,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14432,14 +14432,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14456,7 +14456,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14466,14 +14466,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14483,14 +14483,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -14600,104 +14600,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TMP Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005531238</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-10-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5.199999809265137</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9615384968074835</v>
-      </c>
-      <c r="I2" t="n">
-        <v>153</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14708,129 +14613,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CULTI Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Softlab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>